--- a/stories/arbres/ATOM-SEC.RUE.001-01.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom marche avec papa. Ils vont au marché. Tom sent le pain chaud. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Tom s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Tom sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Papa dit : on s'arrête. Pieds au bord. Sur le trottoir. Tom regarde papa. Il pose les pieds au bord. Les pieds sont calmes. Papa sourit. Papa dit : bravo Tom. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
+          <t>Tom marche avec papa. Ils vont au marché. Tom sent le pain chaud. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Tom s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Tom sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. On s'arrête. Pieds au bord. Sur le trottoir. Tom regarde papa. Il pose les pieds au bord. Les pieds sont calmes. Papa sourit. Bravo Tom. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Tom marche avec papa. Ils vont au marché. Tom sent le pain chaud. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Tom s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Tom sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir.
+papa|On s'arrête. Pieds au bord. Sur le trottoir.
+narrateur|Tom regarde papa. Il pose les pieds au bord. Les pieds sont calmes. Papa sourit.
+papa|Bravo Tom. On s'arrête au trottoir. On attend avec papa.
+narrateur|Les pieds restent au bord du trottoir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Tom arrive au bord. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1842,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Tom donne la main à papa. Ils attendent un moment.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2009,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2049,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-01.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Tom arrive au bord. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Tom s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1847,6 +1855,7 @@
           <t>narrateur|Tom donne la main à papa. Ils attendent un moment.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2014,6 +2023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2066,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2281,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.001-01.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tom s'arrête au trottoir</t>
+          <t>Les oranges d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une caisse d'oranges sent le soleil. Amir et papa vont au marché. Au bord, Amir s'arrête. Pieds au bord, sur le trottoir. Ils attendent. Puis le pain tiède.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom marche avec papa. Ils vont au marché. Tom sent le pain chaud. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Tom s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Tom sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. On s'arrête. Pieds au bord. Sur le trottoir. Tom regarde papa. Il pose les pieds au bord. Les pieds sont calmes. Papa sourit. Bravo Tom. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.</t>
+          <t>Une caisse d'oranges sent le soleil. Les oranges sont rondes et brillantes. Dehors, une gouttière fait tic tic. Le paillasson est encore un peu mouillé. Les chaussures de papa sentent le cuir. Un sac en toile pend au crochet. La maison sent le café tiède. Amir vit ici, avec papa. Papa, ça sent les oranges ! Oui. Le marché est ouvert. Tu mets tes chaussures ? En ce moment, Amir s'assoit. Il enfile la chaussure gauche. Puis la chaussure droite. Les lacets font un petit bruit. Tu as fini tes chaussures ? Oui, papa. Bravo. On prend le sac. Papa ouvre la porte. L'air sent le pain chaud. Une flaque brille sur le trottoir. Elle brille ! Oui. On marche sur le trottoir. Amir donne la main à papa. Ils marchent tout doucement. Le sac tape contre la jambe. Un oiseau crie sur un toit. L'eau de la gouttière chante encore. J'entends le marché ! Bientôt. On reste sur le trottoir. Les oranges sont plus près. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Amir s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Une voiture passe au loin. Amir serre la main de papa. Il sent le pain encore plus fort. Bravo, Amir. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,68 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Tom marche avec papa. Ils vont au marché. Tom sent le pain chaud. Ils arrivent au bord. Le bord du trottoir est là. Papa s'arrête. Tom s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Tom sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir.
-papa|On s'arrête. Pieds au bord. Sur le trottoir.
-narrateur|Tom regarde papa. Il pose les pieds au bord. Les pieds sont calmes. Papa sourit.
-papa|Bravo Tom. On s'arrête au trottoir. On attend avec papa.
+          <t>narrateur|Une caisse d'oranges sent le soleil.
+narrateur|Les oranges sont rondes et brillantes.
+narrateur|Dehors, une gouttière fait tic tic.
+narrateur|Le paillasson est encore un peu mouillé.
+narrateur|Les chaussures de papa sentent le cuir.
+narrateur|Un sac en toile pend au crochet.
+narrateur|La maison sent le café tiède.
+narrateur|Amir vit ici, avec papa.
+enfant-m|Papa, ça sent les oranges !
+papa|Oui.
+papa|Le marché est ouvert.
+papa|Tu mets tes chaussures ?
+narrateur|En ce moment, Amir s'assoit.
+narrateur|Il enfile la chaussure gauche.
+narrateur|Puis la chaussure droite.
+narrateur|Les lacets font un petit bruit.
+papa|Tu as fini tes chaussures ?
+enfant-m|Oui, papa.
+papa|Bravo.
+papa|On prend le sac.
+narrateur|Papa ouvre la porte.
+narrateur|L'air sent le pain chaud.
+narrateur|Une flaque brille sur le trottoir.
+enfant-m|Elle brille !
+papa|Oui.
+papa|On marche sur le trottoir.
+narrateur|Amir donne la main à papa.
+narrateur|Ils marchent tout doucement.
+narrateur|Le sac tape contre la jambe.
+narrateur|Un oiseau crie sur un toit.
+narrateur|L'eau de la gouttière chante encore.
+enfant-m|J'entends le marché !
+papa|Bientôt.
+papa|On reste sur le trottoir.
+narrateur|Les oranges sont plus près.
+narrateur|Le bord du trottoir arrive.
+narrateur|Le bord est gris et net.
+papa|On va s'arrêter.
+papa|Pieds au bord.
+papa|Sur le trottoir.
+narrateur|Amir s'arrête.
+narrateur|Ses pieds sont au bord.
+narrateur|Les pieds restent au bord.
+narrateur|Les pieds sont sur le trottoir.
+enfant-m|Je m'arrête.
+papa|Oui.
+papa|On attend avec papa.
+papa|Tes pieds sont calmes ?
+enfant-m|Oui.
+narrateur|Une voiture passe au loin.
+narrateur|Amir serre la main de papa.
+narrateur|Il sent le pain encore plus fort.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1410,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tom arrive au bord. Que fait-il ?</t>
+          <t>Amir arrive au bord. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1570,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Tom arrive au bord. Que fait-il ?</t>
+          <t>narrateur|Amir arrive au bord.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1599,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+          <t>Amir s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Amir. On attend avec papa. La main de papa est chaude. Le sac de toile est lisse. La flaque brille encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,7 +1747,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Tom s'arrête au bord. Les pieds sont sur le trottoir. Papa est là.</t>
+          <t>narrateur|Amir s'arrête au bord.
+narrateur|Les pieds sont sur le trottoir.
+narrateur|Les pieds restent au bord.
+papa|Tu t'arrêtes au trottoir ?
+enfant-m|Oui.
+enfant-m|Je m'arrête.
+papa|Bravo, Amir.
+papa|On attend avec papa.
+narrateur|La main de papa est chaude.
+narrateur|Le sac de toile est lisse.
+narrateur|La flaque brille encore.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1708,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tom donne la main à papa. Ils attendent un moment.</t>
+          <t>Papa serre doucement la main. On y va ensemble ? Oui, papa. Ils marchent avec l'adulte. Le marché sent le beurre. Une orange brille dans une caisse. Tu prends le pain ? Amir tient le pain tiède. Il est chaud ! Oui. Tu as fini de le tenir ? Oui. Bravo. Le sac devient tout rond. Les oranges sentent encore le soleil.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1852,7 +1929,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Tom donne la main à papa. Ils attendent un moment.</t>
+          <t>narrateur|Papa serre doucement la main.
+papa|On y va ensemble ?
+enfant-m|Oui, papa.
+narrateur|Ils marchent avec l'adulte.
+narrateur|Le marché sent le beurre.
+narrateur|Une orange brille dans une caisse.
+papa|Tu prends le pain ?
+narrateur|Amir tient le pain tiède.
+enfant-m|Il est chaud !
+papa|Oui.
+papa|Tu as fini de le tenir ?
+enfant-m|Oui.
+papa|Bravo.
+narrateur|Le sac devient tout rond.
+narrateur|Les oranges sentent encore le soleil.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1880,7 +1971,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Amir. Le pain sent encore le four. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2020,7 +2111,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Je me suis arrêté.
+papa|Pieds au bord.
+papa|Sur le trottoir.
+papa|Bravo, Amir.
+narrateur|Le pain sent encore le four.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2042,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2176,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-01.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une caisse d'oranges sent le soleil. Les oranges sont rondes et brillantes. Dehors, une gouttière fait tic tic. Le paillasson est encore un peu mouillé. Les chaussures de papa sentent le cuir. Un sac en toile pend au crochet. La maison sent le café tiède. Amir vit ici, avec papa. Papa, ça sent les oranges ! Oui. Le marché est ouvert. Tu mets tes chaussures ? En ce moment, Amir s'assoit. Il enfile la chaussure gauche. Puis la chaussure droite. Les lacets font un petit bruit. Tu as fini tes chaussures ? Oui, papa. Bravo. On prend le sac. Papa ouvre la porte. L'air sent le pain chaud. Une flaque brille sur le trottoir. Elle brille ! Oui. On marche sur le trottoir. Amir donne la main à papa. Ils marchent tout doucement. Le sac tape contre la jambe. Un oiseau crie sur un toit. L'eau de la gouttière chante encore. J'entends le marché ! Bientôt. On reste sur le trottoir. Les oranges sont plus près. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Amir s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Une voiture passe au loin. Amir serre la main de papa. Il sent le pain encore plus fort. Bravo, Amir. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
+          <t>Une caisse d'oranges sent le soleil. Les oranges sont rondes et brillantes. Dehors, une gouttière fait tic tic. Le paillasson est encore un peu mouillé. Les chaussures de papa sentent le cuir. Un sac en toile pend au crochet. La maison sent le café tiède. Amir vit ici, avec papa. Papa, ça sent les oranges ! Oui. Le marché est ouvert. Tu mets tes chaussures ? En ce moment, Amir s'assoit. Il enfile la chaussure gauche. Puis la chaussure droite. Les lacets font un petit bruit. Tu as fini tes chaussures ? Oui, papa. Bravo. On prend le sac. Papa ouvre la porte. L'air sent le pain chaud. Une flaque brille sur le trottoir. Elle brille ! Oui. On marche sur le trottoir. Amir donne la main à papa. Ils marchent tout doucement. Le sac tape contre la jambe. Un oiseau crie sur un toit. L'eau de la gouttière chante encore. J'entends le marché ! Bientôt. On reste sur le trottoir. Les oranges sont plus près. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Amir s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Une voiture passe au loin. Amir serre la main de papa. Il sent le pain encore plus fort. Bravo, Amir. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Tom marche avec papa. Ils vont au marché. Tom sent le pain chaud. Ils arrivent au bord. Le bord du &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt; est là. Papa s'arrête. Tom s'arrête aussi. S'arrêter, c'est le geste. Les pieds de Tom sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Papa dit : on s'arrête. Pieds au bord. Sur le trottoir. Tom regarde papa. Il pose les pieds au bord. Les pieds sont calmes. Papa sourit. Papa dit : bravo Tom. On s'arrête au trottoir. On attend avec papa. Les pieds restent au bord du trottoir.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une caisse d'oranges sent le soleil. Les oranges sont rondes et brillantes. Dehors, une gouttière fait tic tic. Le paillasson est encore un peu mouillé. Les chaussures de papa sentent le cuir. Un sac en toile pend au crochet. La maison sent le café tiède. Amir vit ici, avec papa. Papa, ça sent les oranges ! Oui. Le marché est ouvert. Tu mets tes chaussures ? En ce moment, Amir s'assoit. Il enfile la chaussure gauche. Puis la chaussure droite. Les lacets font un petit bruit. Tu as fini tes chaussures ? Oui, papa. Bravo. On prend le sac. Papa ouvre la porte. L'air sent le pain chaud. Une flaque brille sur le trottoir. Elle brille ! Oui. On marche sur le trottoir. Amir donne la main à papa. Ils marchent tout doucement. Le sac tape contre la jambe. Un oiseau crie sur un toit. L'eau de la gouttière chante encore. J'entends le marché ! Bientôt. On reste sur le trottoir. Les oranges sont plus près. Le bord du trottoir arrive. Le bord est gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Amir s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec papa. Tes pieds sont calmes ? Oui. Une voiture passe au loin. Amir serre la main de papa. Il sent le pain encore plus fort. Bravo, Amir. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1377,7 +1377,6 @@
 narrateur|Amir serre la main de papa.
 narrateur|Il sent le pain encore plus fort.
 papa|Bravo, Amir.
-papa|Tu as fait du bon travail.
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
@@ -1415,7 +1414,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Tom arrive au bord. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir arrive au bord. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1574,7 +1573,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1604,7 +1602,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Tom s'arrête au bord. Les pieds sont sur le &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt;. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Amir. On attend avec papa. La main de papa est chaude. Le sac de toile est lisse. La flaque brille encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1760,7 +1758,6 @@
 narrateur|La flaque brille encore.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1790,7 +1787,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Tom donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à papa. Ils attendent un moment.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa serre doucement la main. On y va ensemble ? Oui, papa. Ils marchent avec l'adulte. Le marché sent le beurre. Une orange brille dans une caisse. Tu prends le pain ? Amir tient le pain tiède. Il est chaud ! Oui. Tu as fini de le tenir ? Oui. Bravo. Le sac devient tout rond. Les oranges sentent encore le soleil.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1946,7 +1943,6 @@
 narrateur|Les oranges sentent encore le soleil.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1971,12 +1967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Amir. Le pain sent encore le four. L'histoire est finie.</t>
+          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Amir. Le pain sent encore le four.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je me suis arrêté. Pieds au bord. Sur le trottoir. Bravo, Amir. Le pain sent encore le four.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2115,11 +2111,9 @@
 papa|Pieds au bord.
 papa|Sur le trottoir.
 papa|Bravo, Amir.
-narrateur|Le pain sent encore le four.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le pain sent encore le four.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2138,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2183,6 +2177,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-01.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trajet vers le marché</t>
+          <t>maison puis trottoir vers le marché, après la pluie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tom, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
